--- a/results/Int All Data -0.3/Rando_fi_explain.xlsx
+++ b/results/Int All Data -0.3/Rando_fi_explain.xlsx
@@ -1676,466 +1676,466 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001194937385512223</v>
+        <v>0.0009708988560259757</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0007035272487532985</v>
+        <v>0.0005491869937395199</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0005196256836713098</v>
+        <v>-0.0006234580185991167</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0003718371085645245</v>
+        <v>-0.000422255256008176</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0002450142279941092</v>
+        <v>0.0005100298513250423</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0001017602127405714</v>
+        <v>0.00131145959012253</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000820199525792641</v>
+        <v>0.0003502161020528684</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0007604791922732111</v>
+        <v>0.0007379689316709103</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0009975030674243067</v>
+        <v>-0.0002132193137733872</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.717004069663357e-05</v>
+        <v>9.792607362537954e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.641958319537063e-05</v>
+        <v>-0.0001308119708293831</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0009639052774465074</v>
+        <v>0.0006436808734521071</v>
       </c>
       <c r="N3" t="n">
-        <v>-7.219713313671899e-05</v>
+        <v>0.0004284663692007619</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.00063285304518499</v>
+        <v>-0.0003911270149681544</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0002105203740010464</v>
+        <v>-0.0002210118708773923</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003899200786187757</v>
+        <v>0.002724697134036387</v>
       </c>
       <c r="R3" t="n">
-        <v>-6.906101574559288e-05</v>
+        <v>0.0004034870841605853</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0003665692310017554</v>
+        <v>0.0009309866970028091</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0004637089012376039</v>
+        <v>0.0003588899362721609</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0001906724659790104</v>
+        <v>0.0006146411735324464</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002015606660232947</v>
+        <v>0.001217189702260442</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0004168350249142747</v>
+        <v>0.0001289859571512908</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0002279457887805968</v>
+        <v>-0.0003529646426875954</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0002404696425266739</v>
+        <v>-0.0001781611217199019</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001648523095062402</v>
+        <v>0.00281318277730002</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001110800318570964</v>
+        <v>0.004518083086989184</v>
       </c>
       <c r="AB3" t="n">
-        <v>-8.993063867486885e-05</v>
+        <v>-0.0003897013647405767</v>
       </c>
       <c r="AC3" t="n">
-        <v>-9.53311380260592e-05</v>
+        <v>0.001332405040743908</v>
       </c>
       <c r="AD3" t="n">
-        <v>-8.647944917736343e-05</v>
+        <v>-0.0004046007097200944</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.006145947122736199</v>
+        <v>0.00358007203628973</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.002004544555391387</v>
+        <v>0.001494777219124959</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.0004475946733730007</v>
+        <v>-0.0003100781064696501</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.000148390489200052</v>
+        <v>-0.0003690787947010444</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.001587049027343308</v>
+        <v>0.001050007520114771</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.003355882041966664</v>
+        <v>0.002300046955175066</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.007432773237670448</v>
+        <v>0.009345781917014793</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.0001881468372909855</v>
+        <v>-0.001151406829131762</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.004936921339656132</v>
+        <v>0.003356781669695136</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.001303822857222122</v>
+        <v>-0.0007386368055071324</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.0003921993965360526</v>
+        <v>0.001052755988258419</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.0006454730897186967</v>
+        <v>-0.0004279825206037591</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.0001928913160733546</v>
+        <v>0.0006629527758649388</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.003978217379148377</v>
+        <v>0.003977118807591846</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0005352414437247655</v>
+        <v>-0.001134647611183874</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.0002050192294414511</v>
+        <v>-0.002563862951229168</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.0005753104820317944</v>
+        <v>-0.000775567906291289</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.0001147822968030898</v>
+        <v>0.0004384898683518723</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.0008454993799906774</v>
+        <v>0.001236450039575041</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.228782113319007e-05</v>
+        <v>0.0002930772448074425</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.00119991303927993</v>
+        <v>0.000277466082742578</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.001576920356652606</v>
+        <v>0.0005830973822770678</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.000997357021959877</v>
+        <v>0.002704494161424258</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.000908515526625321</v>
+        <v>0.00266067069032258</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.0001791600118902981</v>
+        <v>0.0002433737356063626</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.000436144756054061</v>
+        <v>-0.0001169461376202174</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.0003879228493839681</v>
+        <v>-0.0003921017605389632</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.001537841555535851</v>
+        <v>0.002320288876878988</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.001468536886601335</v>
+        <v>-0.001928863867415805</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.0004341252131786588</v>
+        <v>2.092168991410627e-05</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.00196258704616778</v>
+        <v>0.003486837951128834</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0001149920683999906</v>
+        <v>0.0008055294102211086</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.0006269674317324169</v>
+        <v>-0.001974708986178978</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.0002741045362164685</v>
+        <v>5.361380773265643e-05</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.0009766055829350095</v>
+        <v>-0.0002319812233610386</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.0003865424471496315</v>
+        <v>0.001617930952999886</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.001094038494798582</v>
+        <v>-0.0002019175374928173</v>
       </c>
       <c r="BP3" t="n">
-        <v>-7.826054988978575e-06</v>
+        <v>0.001129711536240872</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>8.982035928145616e-06</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.002353619040613163</v>
+        <v>0.004134772154799492</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0001975404841472606</v>
+        <v>0.0001194581729693145</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0.0003933478332672002</v>
+        <v>1.166083169377272e-05</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.001693859519876147</v>
+        <v>0.001256720855208343</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.001099410846531987</v>
+        <v>0.0009131656860732008</v>
       </c>
       <c r="BW3" t="n">
-        <v>-8.907716368705687e-05</v>
+        <v>-8.044927758735778e-06</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0.0005135883129050656</v>
+        <v>-0.0007874317820774412</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.0002106402637614414</v>
+        <v>-0.0009095579840234923</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.0005418691240280749</v>
+        <v>0.0003109911644744212</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0.0004781138260494067</v>
+        <v>-0.0002325729292942147</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0008311309979132885</v>
+        <v>-0.0005135681827419713</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.0004991613975293809</v>
+        <v>0.0005359484732484222</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.007569875138285e-05</v>
+        <v>-5.795307792928249e-05</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.0005277024114271567</v>
+        <v>-0.000434022062984969</v>
       </c>
       <c r="CF3" t="n">
-        <v>-4.23266093318153e-05</v>
+        <v>1.456144733993138e-05</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.0004501633260391857</v>
+        <v>0.0004302605206883203</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0005130183678930656</v>
+        <v>-0.0002060438499747263</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.0007343250626427888</v>
+        <v>0.0005049413415543692</v>
       </c>
       <c r="CJ3" t="n">
-        <v>5.009380757724058e-05</v>
+        <v>-1.640348521204538e-05</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.0003631299379013431</v>
+        <v>-0.0005307705197047863</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0.002252368736171829</v>
+        <v>-0.001972096481032174</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.0003987442121411877</v>
+        <v>-0.0001519937419212901</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.0001190618977097024</v>
+        <v>0.0006533774621464229</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.0003788714286234639</v>
+        <v>0.0003086073966024206</v>
       </c>
       <c r="CP3" t="n">
-        <v>-0.0003132602191266564</v>
+        <v>6.038491890884235e-05</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.0003563014725082925</v>
+        <v>0.001677214989326991</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.002061906731546724</v>
+        <v>-0.0009356099620655013</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.004448097861748836</v>
+        <v>-0.001560267290549063</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0.00202260191325004</v>
+        <v>-0.001453677641638879</v>
       </c>
       <c r="CU3" t="n">
-        <v>-0.0002878762702532878</v>
+        <v>-5.504524334489225e-05</v>
       </c>
       <c r="CV3" t="n">
-        <v>4.770099787807736e-05</v>
+        <v>-7.201971605149681e-05</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>2.994011976048538e-06</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.002824718965398852</v>
+        <v>-0.0008692677046515298</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0.00068344296634148</v>
+        <v>-0.0006582816030189997</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.0004136794360700958</v>
+        <v>-0.0001883797553019162</v>
       </c>
       <c r="DA3" t="n">
-        <v>-2.642255036595654e-06</v>
+        <v>5.756232724772435e-05</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0.0005592669504154935</v>
+        <v>0.0001783043852276478</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0.0008837365721336444</v>
+        <v>-0.002511283816918277</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.0002143392780535536</v>
+        <v>-8.596112402861733e-05</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.0003836058937382681</v>
+        <v>0.0007894003086622126</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.002384008471967729</v>
+        <v>-0.001905900611457469</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.0001745007317243374</v>
+        <v>0.0003248700446841513</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.0005294032646883673</v>
+        <v>-0.001052942330371696</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.0006205592316192354</v>
+        <v>0.0001107286527886431</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.0008553485082192702</v>
+        <v>-0.0006913060696026373</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0.0009312684234918156</v>
+        <v>-0.0007420285814046402</v>
       </c>
       <c r="DL3" t="n">
-        <v>-3.284645584577414e-05</v>
+        <v>0.0002671522273037552</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0.001161957378340302</v>
+        <v>-0.0006406241245801859</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.0004735706848122367</v>
+        <v>0.001477369282698772</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.001585124996006154</v>
+        <v>-0.0004278234989680907</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.0004661755162069726</v>
+        <v>1.791847567569674e-05</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0.0001589028852996866</v>
+        <v>-8.251386329532039e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.0001978599999810038</v>
+        <v>0.0003544992443514061</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.0002799080276568066</v>
+        <v>-4.847475101157461e-05</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0.003169720567568058</v>
+        <v>-1.021658900423714e-05</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0.001558348570718681</v>
+        <v>-0.001220796288293856</v>
       </c>
       <c r="DV3" t="n">
-        <v>-8.8571178604724e-08</v>
+        <v>1.252291781774884e-05</v>
       </c>
       <c r="DW3" t="n">
-        <v>7.33924516763329e-05</v>
+        <v>8.687358155673673e-05</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.0002757825314726815</v>
+        <v>-0.0008300013909848635</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.0006382859485923753</v>
+        <v>0.001103403985512483</v>
       </c>
       <c r="DZ3" t="n">
-        <v>-1.686891775220523e-05</v>
+        <v>-0.0001208188157204826</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.0002680252077211686</v>
+        <v>8.015366039192172e-05</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.0007135999191354269</v>
+        <v>-0.0008719221533122868</v>
       </c>
       <c r="EC3" t="n">
-        <v>-4.559145841439017e-05</v>
+        <v>-0.0006982373502335238</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0.0001767555894038775</v>
+        <v>-0.0006559040988724485</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.0001176800868532279</v>
+        <v>3.127988759725752e-06</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.0001425779590759746</v>
+        <v>-6.032595182193343e-05</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.0006044823943801936</v>
+        <v>-0.0007067309739325035</v>
       </c>
       <c r="EH3" t="n">
-        <v>-3.654662172500766e-05</v>
+        <v>-0.0001056949265470397</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0.0004354073565829387</v>
+        <v>-0.0006495292701577972</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.001039324188645557</v>
+        <v>-0.0002447893339912865</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.0006460337407015248</v>
+        <v>-0.0003804032946320369</v>
       </c>
       <c r="EL3" t="n">
-        <v>1.895978141922105e-05</v>
+        <v>-7.645031349825526e-06</v>
       </c>
       <c r="EM3" t="n">
-        <v>9.024862580528481e-05</v>
+        <v>-7.726319302504225e-05</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.0001014239450001953</v>
+        <v>5.186947500048446e-05</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.0002497506923252946</v>
+        <v>0.0004214708780895016</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.0004967748925624104</v>
+        <v>-0.000388212103812381</v>
       </c>
       <c r="ER3" t="n">
-        <v>-8.030286613155857e-05</v>
+        <v>3.196392743902599e-05</v>
       </c>
       <c r="ES3" t="n">
-        <v>1.171981321825388e-05</v>
+        <v>5.639771822929962e-05</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.0001097698246313739</v>
+        <v>-0.0002293462447937178</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0.001218413669705211</v>
+        <v>-0.0007456454203100284</v>
       </c>
       <c r="EV3" t="n">
-        <v>-3.210410132447495e-05</v>
+        <v>7.932465237057594e-05</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.0004873862542015251</v>
+        <v>-5.27551198488828e-05</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.0009913764155136684</v>
+        <v>-0.001515768797220938</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.0001747389750375827</v>
+        <v>-7.957739116279503e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2145,466 +2145,466 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001647719285668156</v>
+        <v>0.002712216565963374</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002033130314746552</v>
+        <v>0.001820936063289228</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001527758285179919</v>
+        <v>0.001216760452018327</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002123526206315668</v>
+        <v>0.00163411036421483</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001178689901056412</v>
+        <v>0.001093792787491002</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002887998041233407</v>
+        <v>0.004074716169045958</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001535243275235219</v>
+        <v>0.002745345032133156</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00207273888492324</v>
+        <v>0.002659592587991311</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001950739873919818</v>
+        <v>0.002373659241034569</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007625690635666105</v>
+        <v>0.00102855435140711</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004314523162465969</v>
+        <v>0.0006976112868646075</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002393334732334653</v>
+        <v>0.002193979547343286</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007917989386392044</v>
+        <v>0.008031119599120231</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003179499135304961</v>
+        <v>0.001886021395639878</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001258871609649717</v>
+        <v>0.001638505964341104</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.009333323071545337</v>
+        <v>0.007374503728304397</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001204594739128964</v>
+        <v>0.002044379999295992</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003114908852647076</v>
+        <v>0.002462298785436161</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0009109882202780101</v>
+        <v>0.001160337035274148</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001000420996840539</v>
+        <v>0.001471643205668072</v>
       </c>
       <c r="V4" t="n">
-        <v>0.003031717570444903</v>
+        <v>0.002965242843586542</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001783772455501581</v>
+        <v>0.001317025859284427</v>
       </c>
       <c r="X4" t="n">
-        <v>0.00540510400047168</v>
+        <v>0.001015933429505782</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0003725258909523689</v>
+        <v>0.001893627635594145</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.004283324381865406</v>
+        <v>0.004194494898346518</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004479381065470221</v>
+        <v>0.007823145687520112</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0009387798986241699</v>
+        <v>0.0009790020264803735</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.002435964193894711</v>
+        <v>0.002694014090314433</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.004786288282775468</v>
+        <v>0.009309335711784286</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.006236591101423134</v>
+        <v>0.006309225273834369</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.004343661937286069</v>
+        <v>0.005222566281871147</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001216321796210835</v>
+        <v>0.001052548266740668</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0007493315258872094</v>
+        <v>0.001596270959188928</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.005171912076654342</v>
+        <v>0.002463651039233806</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.008296636677194342</v>
+        <v>0.01002073986568788</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01248943034806868</v>
+        <v>0.01662022848839168</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.002119625807281638</v>
+        <v>0.001815884391868704</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.006687002510803161</v>
+        <v>0.004810867983555013</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.001482298849920431</v>
+        <v>0.003474934465615527</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.003755949474303415</v>
+        <v>0.002278762183888588</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0009553536817260312</v>
+        <v>0.001557117240239884</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.002153545363720777</v>
+        <v>0.004029945579626975</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.005525400489433757</v>
+        <v>0.004176931894928551</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.00274340530437709</v>
+        <v>0.002197925524914171</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.004152139833856339</v>
+        <v>0.003561014703631875</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.002094805423204384</v>
+        <v>0.001448043867586994</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.00134516029790812</v>
+        <v>0.002366439513587846</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.001090998246980172</v>
+        <v>0.002250260009404681</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0007067965440451299</v>
+        <v>0.000966191168819637</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.001984635767741727</v>
+        <v>0.001585145804950134</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.003259975293232293</v>
+        <v>0.001265572776810366</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.004513154651043918</v>
+        <v>0.001340996498572043</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.004368712805463914</v>
+        <v>0.00334552417752927</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0004596824430235545</v>
+        <v>0.0005209341267457384</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0007071891147711763</v>
+        <v>0.0009022363848734503</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.002948464615413001</v>
+        <v>0.00240191066642704</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.003724311156237324</v>
+        <v>0.005066035503373498</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.003426584373875299</v>
+        <v>0.006717760211050167</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.001371573925662735</v>
+        <v>0.001041887749233564</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.008506575162879804</v>
+        <v>0.008675262229888714</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.001707669130730444</v>
+        <v>0.003038446462817426</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.003620602326569072</v>
+        <v>0.002998323613801202</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0006959293875621014</v>
+        <v>0.0008990873349710903</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.001164321163297981</v>
+        <v>0.001288285635410611</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.003692483158304982</v>
+        <v>0.003381932459598799</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.001619127447021385</v>
+        <v>0.001834792088111871</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.001951502389741121</v>
+        <v>0.00225668444493946</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>2.840369155840463e-05</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.00334615460121695</v>
+        <v>0.005253054488153132</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.001390217218117357</v>
+        <v>0.001361435088826103</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001692661565351906</v>
+        <v>0.002431554684882069</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.003031378167283772</v>
+        <v>0.001835877346907997</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.002111325393472931</v>
+        <v>0.002266936284767385</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0002289830616569352</v>
+        <v>0.000182359642449311</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.002141508892392239</v>
+        <v>0.001229234188521393</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.002397075015352404</v>
+        <v>0.002342681202089573</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.002639405972902338</v>
+        <v>0.002364380833324033</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.0008331990759619392</v>
+        <v>0.002207069469827343</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.002693130153312134</v>
+        <v>0.003033963884448698</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.001686139725954803</v>
+        <v>0.001692556025074732</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.002034145222037321</v>
+        <v>0.005097869123113239</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.00163675855960035</v>
+        <v>0.001807787694510404</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.001724504994119888</v>
+        <v>0.00280753540411221</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.001587914736597469</v>
+        <v>0.00148153464892558</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001411430938714155</v>
+        <v>0.001501733954482018</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.001608153472974286</v>
+        <v>0.001612559475012863</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0001226046657903449</v>
+        <v>0.000117933655965213</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.001778275292327221</v>
+        <v>0.001905940700063787</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.006656746260303466</v>
+        <v>0.00744153744549838</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.0019114397761092</v>
+        <v>0.001607133900576628</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0009595699687447672</v>
+        <v>0.001204909405038561</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.002344906419493472</v>
+        <v>0.001757159712711161</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0005813140307871517</v>
+        <v>0.0001779462431436904</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.00282779052970847</v>
+        <v>0.002972937745171675</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.005151506613347034</v>
+        <v>0.004355300349618475</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.0100985224953043</v>
+        <v>0.004335494059624649</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.005445612247917305</v>
+        <v>0.007533599637408961</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0003765758716940864</v>
+        <v>0.0003263494881674285</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0002245447727676411</v>
+        <v>0.0002388159358535932</v>
       </c>
       <c r="CW4" t="n">
-        <v>0</v>
+        <v>9.467897186134878e-06</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.008444380194974857</v>
+        <v>0.003360495483760847</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.002103169197279138</v>
+        <v>0.004578684723901175</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0006527382278244381</v>
+        <v>0.0005632440844219144</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0005039295873908523</v>
+        <v>0.0004241285666773144</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.002360195502954558</v>
+        <v>0.001773999614385589</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.00334867799656554</v>
+        <v>0.006570397683055327</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0007238733078569989</v>
+        <v>0.0003627450087989366</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.00222156910891601</v>
+        <v>0.001606176623386292</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.006035145598243352</v>
+        <v>0.004216000720381888</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.001151630913250335</v>
+        <v>0.00121931319294967</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.002664966541526644</v>
+        <v>0.00208098350000425</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.001354038093664947</v>
+        <v>0.001432452221786253</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.002541501709372028</v>
+        <v>0.002542067918469642</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.002212659716513576</v>
+        <v>0.003050262926546247</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0006202473369476959</v>
+        <v>0.0007029901317039951</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.004340570974597609</v>
+        <v>0.003834762718596111</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.001168097127879063</v>
+        <v>0.002786398347499658</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.001317354370217388</v>
+        <v>0.001856551853265109</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.001620417416298238</v>
+        <v>0.001732102884147762</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0004173530645062113</v>
+        <v>0.0003742550517131775</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0004697766898831982</v>
+        <v>0.0005599611749475522</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0007067772676037983</v>
+        <v>0.0001349594624014279</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.004386457484368588</v>
+        <v>0.00299331264755031</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.002941737439278104</v>
+        <v>0.00318799101133846</v>
       </c>
       <c r="DV4" t="n">
-        <v>1.479096740225262e-05</v>
+        <v>2.20591903849634e-05</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0002622811559138141</v>
+        <v>0.000453406211370829</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.001575531864046809</v>
+        <v>0.003208065886724446</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.00215879957318045</v>
+        <v>0.003355278927113339</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0001870347370912842</v>
+        <v>0.0002481615604179244</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.002762592652667955</v>
+        <v>0.002560158928965538</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.002618096466549077</v>
+        <v>0.002004181920984157</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.001296616562143361</v>
+        <v>0.001876144675744079</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.002374189058100869</v>
+        <v>0.002947902238695906</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0002471296657869484</v>
+        <v>0.0001852644518189097</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0008001246843594805</v>
+        <v>0.001742590469501062</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.001537128145167762</v>
+        <v>0.001842546933801821</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0005136012507081559</v>
+        <v>0.0005033797182257937</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.00147322401698095</v>
+        <v>0.00284453187455082</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.004431233604346987</v>
+        <v>0.001193872157440678</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.002636405058734647</v>
+        <v>0.001847797504016866</v>
       </c>
       <c r="EL4" t="n">
-        <v>5.271710953581457e-05</v>
+        <v>9.331367806396276e-05</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0003271185154461243</v>
+        <v>0.0003808617220511606</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0001441773653062502</v>
+        <v>0.0004441489836396556</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.000629605712708144</v>
+        <v>0.0009464443368708092</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.00229863758000096</v>
+        <v>0.00247027533851353</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.000192556579396971</v>
+        <v>8.130564628927288e-05</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0002379176919954458</v>
+        <v>0.0001671131013938507</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.001076021029911698</v>
+        <v>0.001132888986647854</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.002530760911180893</v>
+        <v>0.003470871402836258</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0003452373952522897</v>
+        <v>0.0001425775104815012</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.001052053747778122</v>
+        <v>0.002066126648442244</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.002005299849263593</v>
+        <v>0.002988318234605408</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0006615877950659214</v>
+        <v>0.0005686228890579833</v>
       </c>
     </row>
     <row r="5">
@@ -2614,466 +2614,466 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.001707239962061302</v>
+        <v>-0.003742653881843472</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.005816326530612237</v>
+        <v>-0.001865317736326233</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.004149659863945565</v>
+        <v>-0.003352289733612679</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.004178537511870828</v>
+        <v>-0.002500791389680324</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.001391896071760013</v>
+        <v>-0.001487812598923743</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.004149659863945565</v>
+        <v>-0.001622653515749306</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.002086626620297172</v>
+        <v>-0.001976047904191591</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.00411002213088838</v>
+        <v>-0.003804515929477237</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.004331331014859307</v>
+        <v>-0.005204081632653024</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.001113516857407992</v>
+        <v>-0.001915594133492959</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0008536199810306178</v>
+        <v>-0.001137384016761445</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.003098324375592787</v>
+        <v>-0.002290804963410786</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01970306217135792</v>
+        <v>-0.01339313331271259</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.004773948782801118</v>
+        <v>-0.002880658436214023</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.002210884353741482</v>
+        <v>-0.003095238095238051</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.005058488776478009</v>
+        <v>-0.005754030983243707</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.00217687074829932</v>
+        <v>-0.002687322162503902</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.003185895453139564</v>
+        <v>-0.003464274667491485</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.002515122572429196</v>
+        <v>-0.001666132649791752</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.001677746122190593</v>
+        <v>-0.00321349029589566</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.002660068048252451</v>
+        <v>-0.004515929477265657</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.003435374149659853</v>
+        <v>-0.002036271078587371</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.005221267112384608</v>
+        <v>-0.001972637607381511</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.0003547242824895491</v>
+        <v>-0.003682634730538903</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.003460429349567462</v>
+        <v>-0.002405824628046882</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.005385359561431824</v>
+        <v>-0.006664530599166929</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.002142857142857135</v>
+        <v>-0.002823129251700629</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.005406259879860864</v>
+        <v>-0.001327853303825433</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.007721088435374135</v>
+        <v>-0.01673469387755096</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.0002579812963560579</v>
+        <v>-0.004659863945578202</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.003023046991918577</v>
+        <v>-0.003172702783597714</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.002387774594078351</v>
+        <v>-0.001916167664670632</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.000604902897166526</v>
+        <v>-0.003652694610778406</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.002120924343146579</v>
+        <v>-0.002574079616881164</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.01081632653061224</v>
+        <v>-0.02010204081632649</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.01294456904838198</v>
+        <v>-0.02531239987183593</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.005575136174303152</v>
+        <v>-0.004183673469387717</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.004868795447360075</v>
+        <v>-0.004251700680272075</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.004621715732826837</v>
+        <v>-0.006886227544910151</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.005754030983243752</v>
+        <v>-0.002342513453624606</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.002176870748299309</v>
+        <v>-0.003193171040151721</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.003460429349567484</v>
+        <v>-0.005917912822144477</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.001528175740210158</v>
+        <v>-0.003571428571428537</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.003556552387055489</v>
+        <v>-0.005442176870748283</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.004517782761935307</v>
+        <v>-0.01012495994873437</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.001515620167027576</v>
+        <v>-0.003621670158635126</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.001867679645457432</v>
+        <v>-0.001813553929366885</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.002342513453624584</v>
+        <v>-0.001915594133492959</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.00101796407185627</v>
+        <v>-0.0011972463334331</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.003951944356623449</v>
+        <v>-0.002244836875187062</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.003062171357872012</v>
+        <v>-0.0005986231667165498</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.006417957635156501</v>
+        <v>0.0005389221556886481</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.004710717673095155</v>
+        <v>-0.002260426615727429</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.0006681514476615025</v>
+        <v>-0.0007485029940119458</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.001741057296612891</v>
+        <v>-0.002484286141873682</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.007485029940119736</v>
+        <v>-0.005928143712574818</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.003514995162850732</v>
+        <v>-0.006923806512804276</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.009927284223838118</v>
+        <v>-0.02039203288017701</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.001570009612303802</v>
+        <v>-0.00153796859980776</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.01187084520417853</v>
+        <v>-0.009876543209876553</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.002466013278533041</v>
+        <v>-0.003572557698387568</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.009217445097432775</v>
+        <v>-0.006728612624158936</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.001201391084413506</v>
+        <v>-0.0007903888713246432</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.003129251700680247</v>
+        <v>-0.002449888641425391</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.009910179640718542</v>
+        <v>-0.005907825549025647</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.0004948963810702423</v>
+        <v>-0.003197214308325425</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.002865329512893999</v>
+        <v>-0.002133078637376595</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.001273479783508436</v>
+        <v>-0.0008230452674897303</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.001749920458161036</v>
+        <v>-0.001329534662868026</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.004550898203592802</v>
+        <v>-0.005598802395209546</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.001960164400885223</v>
+        <v>-0.001177968799745266</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.006598639455782318</v>
+        <v>-0.001634091637295754</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.0004761904761904301</v>
+        <v>-0.0004021033096195059</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.003537414965986374</v>
+        <v>-0.003022589882278115</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.003309619548407106</v>
+        <v>-0.004455782312925138</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.005539727761949997</v>
+        <v>-0.003595291123130784</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.001782871696911859</v>
+        <v>-0.005034013605442145</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.00246601327853303</v>
+        <v>-0.006870748299319685</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.003499840916322006</v>
+        <v>-0.001047904191616744</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.003509326588681616</v>
+        <v>-0.009591836734693836</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.003118040089086871</v>
+        <v>-0.002176870748299287</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.003056351480420261</v>
+        <v>-0.004341317365269426</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.001845370664969792</v>
+        <v>-0.002405824628046904</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.0009232728430436321</v>
+        <v>-0.003531876683627644</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.001505927587311817</v>
+        <v>-0.001305316778096122</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-3.2041012495998e-05</v>
+        <v>-0.0002474481905350601</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.001962646407090873</v>
+        <v>-0.003980844058665056</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.02062874251497003</v>
+        <v>-0.02239520958083829</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0.003956948401392824</v>
+        <v>-0.003165558721114292</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.001096420509513096</v>
+        <v>-0.0007271577616186798</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0.003861981639759404</v>
+        <v>-0.002025957581513182</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.001836734693877529</v>
+        <v>-0.0002883691124639598</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.004558404558404549</v>
+        <v>-0.001836734693877506</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.01574850299401195</v>
+        <v>-0.00940119760479039</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.03299401197604789</v>
+        <v>-0.01290419161676644</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.01736526946107784</v>
+        <v>-0.0219760479041916</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0.001074928865001556</v>
+        <v>-0.0005727012408527132</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0.0004138809296402535</v>
+        <v>-0.0005686920083807223</v>
       </c>
       <c r="CW5" t="n">
         <v>0</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0.02652694610778443</v>
+        <v>-0.01017964071856284</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.003547242824895214</v>
+        <v>-0.007874251497005958</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.002196752626552079</v>
+        <v>-0.001530612244897922</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0.0009496676163343043</v>
+        <v>-0.0003502069404647923</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0.004811649256093698</v>
+        <v>-0.002975625197847454</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0.00964071856287424</v>
+        <v>-0.01988023952095804</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0.0004192196065785581</v>
+        <v>-0.0008272351256761068</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0.002659069325735986</v>
+        <v>-0.00119316349564651</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.01919161676646703</v>
+        <v>-0.0136526946107784</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0.001462585034013597</v>
+        <v>-0.0007640878701050235</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.002863506204263466</v>
+        <v>-0.00445434298440982</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.002086626620297172</v>
+        <v>-0.001796407185628701</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.007721088435374135</v>
+        <v>-0.007414965986394517</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0.006428571428571417</v>
+        <v>-0.009149659863945548</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0.001020408163265307</v>
+        <v>-0.001258503401360522</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0.01346938775510205</v>
+        <v>-0.01108843537414963</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0.002513522112631261</v>
+        <v>-0.00264078905504298</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.003786191536748362</v>
+        <v>-0.003911564625850317</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0.004046791021182394</v>
+        <v>-0.002040816326530559</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.0007913896802785869</v>
+        <v>-0.0006462585034013202</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.0001582779360557174</v>
+        <v>-0.0003204101249599356</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.002176870748299298</v>
+        <v>-0.0003592814371257358</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.01170658682634729</v>
+        <v>-0.004104358892777604</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0.006258503401360538</v>
+        <v>-0.00840136054421764</v>
       </c>
       <c r="DV5" t="n">
-        <v>-3.181673560292975e-05</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0.0002845399936768689</v>
+        <v>-0.0004190362167015849</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.004013605442176849</v>
+        <v>-0.00952380952380949</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0.004040725421571789</v>
+        <v>-0.003531876683627644</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.000340136054421758</v>
+        <v>-0.0003844921499519427</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.007142857142857129</v>
+        <v>-0.005850340136054388</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.004931972789115635</v>
+        <v>-0.004899777282850804</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0.001877187400572733</v>
+        <v>-0.00499999999999996</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0.006428571428571406</v>
+        <v>-0.008843537414965952</v>
       </c>
       <c r="EE5" t="n">
-        <v>-6.323110970596346e-05</v>
+        <v>-0.000389221556886199</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0.000986946832219071</v>
+        <v>-0.003401360544217647</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.004251700680272097</v>
+        <v>-0.005510204081632619</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0.001297879075656882</v>
+        <v>-0.001281640499839798</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.002312925170068014</v>
+        <v>-0.006700680272108783</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.01357142857142857</v>
+        <v>-0.002517006802721045</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0.007006802721088423</v>
+        <v>-0.004999999999999971</v>
       </c>
       <c r="EL5" t="n">
-        <v>-3.401360544217358e-05</v>
+        <v>-0.0001934859722669713</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0.0004138809296402535</v>
+        <v>-0.0009545020680878147</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0.0001360544217686943</v>
+        <v>-0.0004454342984410053</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.0002213088839708832</v>
+        <v>-0.001047590541753962</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0.005136054421768699</v>
+        <v>-0.006530612244897938</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.0006122448979591244</v>
+        <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.0005442176870747772</v>
+        <v>-0.0001281640499839809</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0.001360544217687043</v>
+        <v>-0.001666666666666628</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.007346938775510192</v>
+        <v>-0.009625850340136011</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0.0008503401360544172</v>
+        <v>-3.401360544215137e-05</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0.001044634377967735</v>
+        <v>-0.004489795918367323</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.006054421768707463</v>
+        <v>-0.009727891156462564</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.0008682634730538763</v>
+        <v>-0.0014537581193937</v>
       </c>
     </row>
     <row r="6">
@@ -3083,466 +3083,466 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002322973405959244</v>
+        <v>0.0005255057589130558</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0009119497111830799</v>
+        <v>-0.0009898215044165353</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0008709874973079596</v>
+        <v>-0.001125239536219116</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.001195335899025285</v>
+        <v>-0.001253674257269982</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.000487302233333975</v>
+        <v>-0.0001057388565752687</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.00143185946180186</v>
+        <v>-0.001310601554930691</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001870854220920704</v>
+        <v>-0.001350994908463143</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.00194982345814188</v>
+        <v>-0.000788695638163342</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.001852163020896969</v>
+        <v>-0.001576789706962792</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0006245344069695485</v>
+        <v>-0.0004772510340439073</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0002326469509959573</v>
+        <v>-0.0005298442706297591</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0002591494273529255</v>
+        <v>-0.0006625557962852968</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.002017560239535013</v>
+        <v>-0.003914062785629236</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.002581577677464272</v>
+        <v>-0.001317598490061006</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0007437488286152649</v>
+        <v>-0.0003574575245004097</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0013242941196906</v>
+        <v>-0.001182498653599379</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.00074710266077532</v>
+        <v>-0.0007969255362778205</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.001554459604418912</v>
+        <v>-0.0002840176777085923</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0007404119334472881</v>
+        <v>-5.496841075682823e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.000254797965655848</v>
+        <v>0.0004544422400309834</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0002445776706412023</v>
+        <v>0.0004491049174451423</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.001257840444467201</v>
+        <v>-0.0005302802229253639</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.003230973440263493</v>
+        <v>-0.001170358712773894</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.690993400240373e-05</v>
+        <v>-0.000704009951391088</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.002144814052263264</v>
+        <v>0.0008162107319525103</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.002049014391256418</v>
+        <v>0.0002873202049198775</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0003952745003786368</v>
+        <v>-0.000458768573178972</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.0009174199542898081</v>
+        <v>-0.0005709586651910931</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.003368883469654643</v>
+        <v>-0.004021306550489439</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.001177199847757573</v>
+        <v>-0.0005160542876504665</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.001414635950238571</v>
+        <v>-0.002059390613934167</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.001338697459707139</v>
+        <v>-0.0009012940297766919</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0004129637254007584</v>
+        <v>-0.0007076634265443776</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.0005009511660749061</v>
+        <v>-0.0003764302344408138</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0001099638838072819</v>
+        <v>2.18369129544177e-05</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.001346938689180724</v>
+        <v>0.0002405004317985682</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0003166853611733689</v>
+        <v>-0.00182318322179974</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.001959242977155848</v>
+        <v>0.0005458487095118842</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.001802924410474718</v>
+        <v>-0.002661382269787247</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.002324295953118716</v>
+        <v>-0.000306317913879256</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.001324058111857093</v>
+        <v>-0.001411556066472558</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.0004878431031941327</v>
+        <v>-0.001257880864013516</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.0005597455058202055</v>
+        <v>0.0009282712817966082</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0008934512702922781</v>
+        <v>-0.002731849978582173</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.00341663896153622</v>
+        <v>-0.003821682601405552</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.0006932214091825678</v>
+        <v>-0.001049440254076639</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.001300346445717349</v>
+        <v>-0.001063322221556659</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.001855791894694278</v>
+        <v>-0.0001423000211070308</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0003643860333744531</v>
+        <v>-0.0003319933502249711</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.002503825312359909</v>
+        <v>-0.0008390544684718616</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.0005969055203823376</v>
+        <v>-0.0004524179782295801</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.0004070065405301304</v>
+        <v>0.001789251669693459</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.002073396160272506</v>
+        <v>0.0007861401202259255</v>
       </c>
       <c r="BC6" t="n">
-        <v>9.326823057046463e-05</v>
+        <v>-4.639653572531544e-05</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0008710998302472572</v>
+        <v>-0.0001187244104997265</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.000622967850070802</v>
+        <v>-0.000810119673375001</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.001201642461243207</v>
+        <v>-0.0004532365399558397</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.002525107024749876</v>
+        <v>-0.00120497339336878</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.0004828268184175171</v>
+        <v>-0.0006125278725644945</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.00472853725802104</v>
+        <v>-0.002854210196296253</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.001287757700979147</v>
+        <v>-0.0007880947893918189</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.001843396597170435</v>
+        <v>-0.003696530440585502</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0006594344020851739</v>
+        <v>-0.0005645299658562198</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.001792055053008476</v>
+        <v>-0.0004484680635467364</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.001029221690666204</v>
+        <v>0.0001807330258761036</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.0001737429149081565</v>
+        <v>-0.001239505879602557</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.001504604106853763</v>
+        <v>-0.0003032077498517083</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.0001784385702196745</v>
+        <v>0.0001117374816496125</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.001154137889656195</v>
+        <v>-0.0009876166035276079</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0004670779486579735</v>
+        <v>-0.0002228387031291801</v>
       </c>
       <c r="BU6" t="n">
-        <v>-1.879625318658708e-05</v>
+        <v>-0.0001296454427361149</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.0009758616669794356</v>
+        <v>-0.0004903025184116033</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.0002055211227234705</v>
+        <v>-3.164557912159749e-05</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.002561647330985137</v>
+        <v>-0.001526293726911374</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.001470476557088815</v>
+        <v>-0.002175693737705145</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.00149271221580588</v>
+        <v>-0.0009955207295139407</v>
       </c>
       <c r="CA6" t="n">
-        <v>-0.001151407381566097</v>
+        <v>-0.0009585425532986191</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0007505516681260816</v>
+        <v>-0.0006974145711282215</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.001772272527884314</v>
+        <v>-0.0008740951647436907</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.0002027320374448915</v>
+        <v>-0.001015462220312835</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.001819085621058025</v>
+        <v>-0.002093949280529539</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.001306038808966245</v>
+        <v>-0.002018164954615986</v>
       </c>
       <c r="CG6" t="n">
-        <v>-1.448912010494352e-05</v>
+        <v>-0.0004214640151284005</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0006098968163271657</v>
+        <v>-0.0007664457660614077</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.0002956186859379206</v>
+        <v>-0.0007236808024450814</v>
       </c>
       <c r="CJ6" t="n">
+        <v>-3.199000801892559e-05</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>-0.001377601753319521</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>-0.0008739127645339239</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>-0.001171850592057017</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>-0.000514482405628594</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>-0.001095085840278448</v>
+      </c>
+      <c r="CP6" t="n">
         <v>0</v>
       </c>
-      <c r="CK6" t="n">
-        <v>-0.0005874444308232168</v>
-      </c>
-      <c r="CL6" t="n">
-        <v>-0.002056832304796033</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>0.000188983533291906</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>-0.0008637302165109828</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>-0.001002557328920317</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>-0.0004037757374635908</v>
-      </c>
       <c r="CQ6" t="n">
-        <v>-0.00234461296485535</v>
+        <v>-0.0005094476256115228</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.002004606210955423</v>
+        <v>-0.003840412233269364</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0.002543948934416796</v>
+        <v>-0.001449628816684589</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0.0009841355590039097</v>
+        <v>-0.001140825639392984</v>
       </c>
       <c r="CU6" t="n">
-        <v>-0.000371683918681201</v>
+        <v>-0.0002324960769036905</v>
       </c>
       <c r="CV6" t="n">
-        <v>-2.498001805406602e-17</v>
+        <v>-0.0002098112073181141</v>
       </c>
       <c r="CW6" t="n">
         <v>0</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0.001570880365085989</v>
+        <v>-0.0004068456827710453</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0.002586564566844257</v>
+        <v>-0.003877692030569601</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.0003980720190980474</v>
+        <v>-0.0003480479030512323</v>
       </c>
       <c r="DA6" t="n">
-        <v>-0.0002551020408163129</v>
+        <v>-0.0002055571218092495</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0.001191520825819442</v>
+        <v>-0.00106072652565179</v>
       </c>
       <c r="DC6" t="n">
-        <v>-0.001357431085296679</v>
+        <v>-0.001045586766694709</v>
       </c>
       <c r="DD6" t="n">
-        <v>-0.000228357108889013</v>
+        <v>-0.0002574167202697458</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0.0008032668654854331</v>
+        <v>-0.0002069958247537668</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.001555749493262051</v>
+        <v>-0.001469251563307258</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0.0007009216879838243</v>
+        <v>-0.0006514776249990417</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.001355801409843782</v>
+        <v>-0.002147145391107696</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.00162929365914905</v>
+        <v>-0.001202565213735435</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.0007704771861395177</v>
+        <v>-0.0007933706068855878</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0.00119704439945249</v>
+        <v>-0.0003892650043350626</v>
       </c>
       <c r="DL6" t="n">
-        <v>-0.0001829563592092381</v>
+        <v>4.001354013895009e-05</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0.0001267703675529225</v>
+        <v>-2.371166613971964e-05</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0.0007669845494196913</v>
+        <v>-0.0005404982278263942</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.002621722082085024</v>
+        <v>-0.001415288827913072</v>
       </c>
       <c r="DP6" t="n">
-        <v>-0.001431633302795818</v>
+        <v>-0.00105199794227536</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.0004964047941033056</v>
+        <v>-0.0003239468992091599</v>
       </c>
       <c r="DR6" t="n">
-        <v>-7.964242938230947e-05</v>
+        <v>7.630989069559726e-06</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.0003165158397532731</v>
+        <v>0</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0.004713819826371523</v>
+        <v>-0.00210681991961841</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0.003950713929419885</v>
+        <v>-0.002425533425299345</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-8.444450904766809e-05</v>
+        <v>-0.0001191525081668032</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.0002394604684674284</v>
+        <v>-0.0007880552574933669</v>
       </c>
       <c r="DY6" t="n">
-        <v>-0.001375685017106312</v>
+        <v>-0.0005273358179201882</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.0001113687041026518</v>
+        <v>-0.0003129924637529508</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.0009783950082672215</v>
+        <v>-0.0006840699449553289</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.002490013709209551</v>
+        <v>-0.001944832063879659</v>
       </c>
       <c r="EC6" t="n">
-        <v>-0.0009096668811612279</v>
+        <v>-0.001490409917548627</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0.0002048940731446625</v>
+        <v>-0.0002395097563029941</v>
       </c>
       <c r="EE6" t="n">
         <v>0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.0004688536920658015</v>
+        <v>-0.001289215949939218</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.0002262210653002139</v>
+        <v>-0.0007775149477791065</v>
       </c>
       <c r="EH6" t="n">
-        <v>-5.585652300686972e-05</v>
+        <v>-0.0003012250745570155</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.001225423009418503</v>
+        <v>-0.0007319812606694815</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.0001831676576633801</v>
+        <v>-0.000868144147162564</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.0007396239651068226</v>
+        <v>-0.0005323329875410205</v>
       </c>
       <c r="EL6" t="n">
-        <v>0</v>
+        <v>-2.319826786266188e-05</v>
       </c>
       <c r="EM6" t="n">
-        <v>-8.542259719359069e-05</v>
+        <v>-0.0001109764956715581</v>
       </c>
       <c r="EN6" t="n">
-        <v>7.954183900729662e-06</v>
+        <v>-0.0001597232808739218</v>
       </c>
       <c r="EO6" t="n">
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-9.897898099676117e-05</v>
+        <v>-0.0001367365100933437</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0.001060784840950077</v>
+        <v>-0.0007890801803283526</v>
       </c>
       <c r="ER6" t="n">
-        <v>-7.754898748874305e-05</v>
+        <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-2.40307593719985e-05</v>
+        <v>0</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.000613176871052143</v>
+        <v>-0.0007942549565669116</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0.001926462298665646</v>
+        <v>-0.0008264885808057953</v>
       </c>
       <c r="EV6" t="n">
-        <v>-0.0001659816629781457</v>
+        <v>-3.177644850498318e-05</v>
       </c>
       <c r="EW6" t="n">
-        <v>2.948357672637735e-05</v>
+        <v>-0.0003952734876249891</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0.001541678638843782</v>
+        <v>-0.001016511117076366</v>
       </c>
       <c r="EY6" t="n">
-        <v>-9.674298613351341e-05</v>
+        <v>-0.0001506087098050779</v>
       </c>
     </row>
     <row r="7">
@@ -3552,298 +3552,298 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00128149478054026</v>
+        <v>0.00163887112299812</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0003168279831762877</v>
+        <v>0.001013834783676076</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0004596062600847883</v>
+        <v>-0.0004448108873450929</v>
       </c>
       <c r="E7" t="n">
-        <v>-9.026100470003746e-05</v>
+        <v>-0.0007285298447473666</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0002142320515185148</v>
+        <v>0.0002788220702450217</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000299769598284666</v>
+        <v>-0.000120825841690525</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008499340519397714</v>
+        <v>-0.000236756370173996</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0007164903903841223</v>
+        <v>0.0005239143098458632</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0005784829594596531</v>
+        <v>0.0005689731192278947</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.141437410304481e-05</v>
+        <v>0.0003133871066376248</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001568750964426269</v>
+        <v>-0.0001913313400591199</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0009372865628834992</v>
+        <v>0.0003142771625261942</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003176065077415879</v>
+        <v>0.002638600544851122</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0006353117663962736</v>
+        <v>-0.0004791902030309825</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.0002060433527878047</v>
+        <v>-0.0001745498708955795</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.00137453477793823</v>
+        <v>0.001315690247200957</v>
       </c>
       <c r="R7" t="n">
-        <v>-5.986231667164943e-05</v>
+        <v>0.0008730683515783932</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0005078342467349894</v>
+        <v>0.0009547654348900203</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0001556912927427434</v>
+        <v>0.0002371166613974407</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0001346902125112015</v>
+        <v>0.0009089549866949709</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001943651049584616</v>
+        <v>0.0007161297883756634</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0001611466152840635</v>
+        <v>-5.743155049826588e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.00132650209189451</v>
+        <v>-0.0002209666184528225</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001317012000597695</v>
+        <v>4.748338081673187e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001011309776322567</v>
+        <v>0.002428698563679177</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001758317049963759</v>
+        <v>0.002867489880383889</v>
       </c>
       <c r="AB7" t="n">
-        <v>-8.961424641237901e-09</v>
+        <v>-0.0002864316563654712</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0005538250048839844</v>
+        <v>0.001077698942243177</v>
       </c>
       <c r="AD7" t="n">
-        <v>-7.485029940120792e-05</v>
+        <v>0.001535891921982246</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.003974872399648676</v>
+        <v>0.002480821832119234</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.001645672169836709</v>
+        <v>-0.000150261004501484</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.0003997700882439226</v>
+        <v>-0.0004996060431328552</v>
       </c>
       <c r="AH7" t="n">
-        <v>-9.896779490373712e-05</v>
+        <v>-0.0001883040552137616</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.0001352259909503717</v>
+        <v>0.000366054531311949</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.002639125110600993</v>
+        <v>0.003147304355215391</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.01134948250826833</v>
+        <v>0.01267073675652031</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.165558721113237e-05</v>
+        <v>-0.001106297433785686</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.004051250414400293</v>
+        <v>0.001150573599004279</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.001242732681964531</v>
+        <v>-5.974649148604615e-06</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.0007522180143053669</v>
+        <v>0.0008377957318301599</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.0007197642952074479</v>
+        <v>-0.0001586050337672451</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0007158336842065016</v>
+        <v>0.0004584139397282361</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.003758614685450362</v>
+        <v>0.004268973922999209</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0005162867650028713</v>
+        <v>-0.000474573597839123</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.0002887198063512064</v>
+        <v>-0.00166368186312707</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.0001738855516914606</v>
+        <v>-0.0005003726293589638</v>
       </c>
       <c r="AV7" t="n">
-        <v>-3.264916281703331e-06</v>
+        <v>-0.000221751763440331</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.000744958496657705</v>
+        <v>0.0006582023997148079</v>
       </c>
       <c r="AX7" t="n">
-        <v>-4.810786331557183e-05</v>
+        <v>0.0001723349104579885</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.001822608344564436</v>
+        <v>0.0001706756253324559</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0008624874172827035</v>
+        <v>0.0002226540233764007</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0005537800635525503</v>
+        <v>0.00265979025410214</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.0004728476780236578</v>
+        <v>0.003007956739550305</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.000229009966457433</v>
+        <v>0.0001745592481027292</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.000402168138833131</v>
+        <v>-1.700680272107014e-05</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0009015928955147578</v>
+        <v>-0.0007187635354176547</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.001062366949027249</v>
+        <v>0.001667372756860452</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.0003677539391824913</v>
+        <v>-0.0003816384703057895</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.0005530217185170105</v>
+        <v>-3.803892131618025e-05</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.002501719778987827</v>
+        <v>0.002973276078200698</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0003247757500772941</v>
+        <v>-6.223665307661386e-05</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0002900223088519616</v>
+        <v>-0.002020650057908868</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0.0004293550165981264</v>
+        <v>-0.0003729693310324578</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.0005388798890137991</v>
+        <v>-6.367398917540013e-05</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0009241091169322924</v>
+        <v>0.001528957133073405</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0006136962829802972</v>
+        <v>0.0005429029972873589</v>
       </c>
       <c r="BP7" t="n">
-        <v>2.991771619885731e-05</v>
+        <v>0.000868163544074163</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.001330952225340026</v>
+        <v>0.002527413478956747</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0004942169147855279</v>
+        <v>-0.0003982926788417107</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0.0001997258158088267</v>
+        <v>0.0001849278237875451</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.001247049263490219</v>
+        <v>0.001445720635870251</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.000531645918693946</v>
+        <v>0.0004329352389536523</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-1.496557916791375e-05</v>
       </c>
       <c r="BX7" t="n">
-        <v>9.018933021925956e-06</v>
+        <v>-0.0004673880124338003</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0005073385761193983</v>
+        <v>-0.001143111355504384</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.0002236802970275842</v>
+        <v>0.0003942462748750986</v>
       </c>
       <c r="CA7" t="n">
-        <v>-0.0003587871635566675</v>
+        <v>-0.0001263621385165392</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.0006856277611231087</v>
+        <v>-4.966427239147531e-05</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0001458441191753646</v>
+        <v>-9.739322150824619e-05</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0004953095772840422</v>
+        <v>-0.0006543354918163602</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.000248038267225631</v>
+        <v>-0.0005533829297946269</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.0003892240973346228</v>
+        <v>0.0002364321303613304</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0003216500222509467</v>
+        <v>0.0005009563367568248</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0004016155884728534</v>
+        <v>6.508739892236993e-05</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.0003849969871925707</v>
+        <v>0.000203096980122347</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0</v>
+        <v>-3.087394696937862e-05</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.000110927648168635</v>
+        <v>-0.000878521658556769</v>
       </c>
       <c r="CL7" t="n">
-        <v>-1.391065208784515e-05</v>
+        <v>-0.0004604023925486922</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.0006391357339287307</v>
+        <v>-0.0002742854543918538</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.0004112223910586854</v>
+        <v>0.0007653386336951007</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0005536928818000609</v>
+        <v>0.0001127042359686414</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.0001892100259846374</v>
+        <v>6.363347120587059e-05</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.0003957321151666304</v>
+        <v>0.001341667251740736</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.000934149275193763</v>
+        <v>-0.0002096098032892291</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0.001347885877000704</v>
+        <v>-0.0003181646121486914</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0.0005586417948268141</v>
+        <v>3.520511079064821e-05</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.0001410010156616515</v>
+        <v>-3.183699458770839e-05</v>
       </c>
       <c r="CV7" t="n">
         <v>1.582779360557174e-05</v>
@@ -3852,166 +3852,166 @@
         <v>0</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0.0003349375767139229</v>
+        <v>6.033816644698267e-05</v>
       </c>
       <c r="CY7" t="n">
-        <v>-0.0005611869876342324</v>
+        <v>6.412750761687348e-05</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.0002597785170362632</v>
+        <v>0</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.612383102224668e-05</v>
+        <v>-7.799267707981894e-05</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.0001056014480009526</v>
+        <v>0.0007989267928700972</v>
       </c>
       <c r="DC7" t="n">
-        <v>-8.811659523073613e-05</v>
+        <v>-0.0003338757491114341</v>
       </c>
       <c r="DD7" t="n">
-        <v>-2.775557561562891e-17</v>
+        <v>3.2041012495998e-05</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0.0001745700827275265</v>
+        <v>9.764707664804418e-05</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.0009234176991757936</v>
+        <v>-0.0008275586554570835</v>
       </c>
       <c r="DG7" t="n">
-        <v>4.8450271167394e-05</v>
+        <v>-4.608233796604683e-06</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.000104308668676234</v>
+        <v>-0.000869988211471323</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.001253618662675865</v>
+        <v>0.0001704829126900232</v>
       </c>
       <c r="DJ7" t="n">
-        <v>-0.0002858638481124332</v>
+        <v>-6.511132527415309e-05</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0.0006363280988661013</v>
+        <v>-0.0001744685444144078</v>
       </c>
       <c r="DL7" t="n">
-        <v>-4.767609345915358e-05</v>
+        <v>9.369904222150116e-05</v>
       </c>
       <c r="DM7" t="n">
-        <v>7.693774999972258e-05</v>
+        <v>0.0003619067563965017</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0.00035379435952127</v>
+        <v>0.001680339513822987</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.001099478568724832</v>
+        <v>-0.0002423787487068396</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.0001780204603585134</v>
+        <v>-0.0002867386800085581</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-3.224766204452112e-05</v>
+        <v>-9.512791002521669e-05</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.238509850890807e-05</v>
+        <v>0.0002478981335463981</v>
       </c>
       <c r="DS7" t="n">
-        <v>-4.816484351825023e-05</v>
+        <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>-0.0012071753873728</v>
+        <v>-0.00012081356244526</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0.0001289906481780234</v>
+        <v>-0.0007324562092457021</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>1.158251854321833e-06</v>
+        <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-6.321071915171812e-07</v>
+        <v>3.137387970990613e-05</v>
       </c>
       <c r="DY7" t="n">
-        <v>-0.0004960559722464509</v>
+        <v>6.377205066925294e-05</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-4.575895194139923e-05</v>
+        <v>-0.0001884843964783389</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.0003062610944842836</v>
+        <v>0.0001267782730077272</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.0003984875417596623</v>
+        <v>-0.0005280646524590481</v>
       </c>
       <c r="EC7" t="n">
-        <v>-0.0001938979184487932</v>
+        <v>-0.0004027616287333225</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.00031667596918592</v>
+        <v>1.358956156261029e-06</v>
       </c>
       <c r="EE7" t="n">
-        <v>1.582779360557174e-05</v>
+        <v>0</v>
       </c>
       <c r="EF7" t="n">
-        <v>6.802721088434715e-05</v>
+        <v>0.0002545047068027217</v>
       </c>
       <c r="EG7" t="n">
-        <v>-2.220446049250313e-17</v>
+        <v>-0.0002225852568999154</v>
       </c>
       <c r="EH7" t="n">
-        <v>-1.49655791679304e-05</v>
+        <v>-4.820794421096508e-05</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0.0004975535164283506</v>
+        <v>-0.0001117085653013994</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.0001389012038041371</v>
+        <v>-0.0001278368770359639</v>
       </c>
       <c r="EK7" t="n">
-        <v>4.593423052894898e-05</v>
+        <v>9.555883646679142e-05</v>
       </c>
       <c r="EL7" t="n">
         <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>3.098608541589609e-05</v>
+        <v>-1.582779360557174e-05</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.0001081278472097269</v>
+        <v>-6.334182957332124e-05</v>
       </c>
       <c r="EO7" t="n">
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-1.590836780147042e-05</v>
+        <v>0.0003005046583350879</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0.0007536393337009561</v>
+        <v>4.658113402091768e-05</v>
       </c>
       <c r="ER7" t="n">
-        <v>-1.496557916791375e-05</v>
+        <v>0</v>
       </c>
       <c r="ES7" t="n">
-        <v>1.591849729385419e-05</v>
+        <v>0</v>
       </c>
       <c r="ET7" t="n">
-        <v>-1.509716238030088e-05</v>
+        <v>-0.0003970050624117927</v>
       </c>
       <c r="EU7" t="n">
-        <v>-7.71443995482568e-05</v>
+        <v>-9.238011832045645e-05</v>
       </c>
       <c r="EV7" t="n">
-        <v>0</v>
+        <v>1.546551190844681e-05</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.0005006535076794161</v>
+        <v>-0.0002224160826445054</v>
       </c>
       <c r="EX7" t="n">
-        <v>-0.0002564730538105409</v>
+        <v>-0.0007045393878698181</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.0001686208327712768</v>
+        <v>4.777941823339571e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4021,466 +4021,466 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002407278445821018</v>
+        <v>0.002354607520561824</v>
       </c>
       <c r="C8" t="n">
-        <v>0.000101025760145404</v>
+        <v>0.001692031559753127</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001425941012244775</v>
+        <v>4.416700159844966e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001248448661416413</v>
+        <v>0.0002477444189729505</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0004185045480970151</v>
+        <v>0.001466236413757074</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000753458253725256</v>
+        <v>0.001765193138298524</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001469642213533309</v>
+        <v>0.001001799470039869</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006736459735422946</v>
+        <v>0.001947182936379993</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0006684705266718161</v>
+        <v>0.001320325638827011</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0003962929478795674</v>
+        <v>0.0005308542459241256</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002409693530837004</v>
+        <v>0.0002242360829948997</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001355410752181557</v>
+        <v>0.001491438455724148</v>
       </c>
       <c r="N8" t="n">
-        <v>0.004646737527871697</v>
+        <v>0.006353101980208964</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00118851944611259</v>
+        <v>0.0001432664756447294</v>
       </c>
       <c r="P8" t="n">
-        <v>0.000465293924932339</v>
+        <v>0.0001634320286121455</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.006200525718115216</v>
+        <v>0.005096387321349571</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0005204037530971789</v>
+        <v>0.0016060616596905</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002221861080821841</v>
+        <v>0.002648923425703209</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0001035882708184888</v>
+        <v>0.0007027052065962658</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001105115861242911</v>
+        <v>0.001302301114622023</v>
       </c>
       <c r="V8" t="n">
-        <v>0.005046467675530261</v>
+        <v>0.002341922976341756</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0006960958061025424</v>
+        <v>0.000971304156340419</v>
       </c>
       <c r="X8" t="n">
-        <v>0.00165771146221714</v>
+        <v>0.00055469465723256</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0005067714050639078</v>
+        <v>0.0004556271483711543</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.004416820812217126</v>
+        <v>0.003114947864808928</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003703043233996345</v>
+        <v>0.01091972220948236</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0003777249813085026</v>
+        <v>0.0003239571801606749</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.001179090898240839</v>
+        <v>0.00212562304304891</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.001637283630366215</v>
+        <v>0.004542600979408225</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.01132371340077199</v>
+        <v>0.007414262940724748</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.003101639975507684</v>
+        <v>0.002379320704925825</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0001536638257000761</v>
+        <v>0.0002189961763486653</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0006702505313616686</v>
+        <v>0.0003244497527351425</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.001381731942843184</v>
+        <v>0.002275838054790555</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.006082906166020354</v>
+        <v>0.006678780523585367</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.01523356857637578</v>
+        <v>0.02025721081034582</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0008265309930512943</v>
+        <v>-0.0001281640499839643</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.006348995057348638</v>
+        <v>0.008232653330534287</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.0003637935468965292</v>
+        <v>0.001750124663933877</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0004923044011304611</v>
+        <v>0.001963124272668704</v>
       </c>
       <c r="AP8" t="n">
-        <v>-8.752134663906064e-05</v>
+        <v>0.0002095548687180898</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.00162892222416032</v>
+        <v>0.003013250645963297</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.004568357677467885</v>
+        <v>0.007097598526888005</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.001262904613466884</v>
+        <v>0.0004824829282971871</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0005296305611315777</v>
+        <v>-0.0008485103279754713</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.0005742964022254993</v>
+        <v>-2.387774594077297e-05</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0007375330875480979</v>
+        <v>0.001067455198783845</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0001479060270872717</v>
+        <v>0.002872265672736185</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0003355634243169897</v>
+        <v>0.0007284229895132055</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0006190759640443632</v>
+        <v>0.001534702968046933</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.003400805157795964</v>
+        <v>0.001220072905889475</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.002258873439846823</v>
+        <v>0.00382617529442929</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.003226517784605615</v>
+        <v>0.003804891013391634</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0003108697375238001</v>
+        <v>0.0007134040281527338</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.847573689396148e-05</v>
+        <v>0.0003424984041434958</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.001023518184727265</v>
+        <v>0.000450764772271961</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.004130194606148028</v>
+        <v>0.006198840795215726</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.0004526065572820454</v>
+        <v>0.0005844901661162805</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.001290348517630541</v>
+        <v>0.0003914871354802229</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.008052936588242797</v>
+        <v>0.009327690112177378</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.001431922055082318</v>
+        <v>0.002565767878447414</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.001565050414929462</v>
+        <v>-0.0008175529046384217</v>
       </c>
       <c r="BL8" t="n">
-        <v>-9.903947132026969e-05</v>
+        <v>0.0005567584287040101</v>
       </c>
       <c r="BM8" t="n">
-        <v>-0.0002608512417281161</v>
+        <v>0.0002192102025768139</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.001877071273916311</v>
+        <v>0.003984603678713295</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.002072052817333087</v>
+        <v>0.0008459444725972016</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.001057973361013276</v>
+        <v>0.002417498884302649</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.002726713179999981</v>
+        <v>0.007298026897025653</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.001172217417743437</v>
+        <v>0.00142838893310811</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0006809598242117576</v>
+        <v>0.001162081810727636</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.002730609403572718</v>
+        <v>0.001812848662992927</v>
       </c>
       <c r="BV8" t="n">
-        <v>-0.0003857678452104801</v>
+        <v>0.001511998436601642</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.326672684688675e-18</v>
+        <v>6.599046804352804e-05</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.001249935029671295</v>
+        <v>0.0002302431008224859</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.002033165717424415</v>
+        <v>4.565430741388656e-05</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.001217265102152501</v>
+        <v>0.001916281328454775</v>
       </c>
       <c r="CA8" t="n">
-        <v>-0.0001099823893007612</v>
+        <v>0.000891444550970752</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.001029048701050575</v>
+        <v>0.0003647137471766398</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0006625508090193022</v>
+        <v>0.001708818697155201</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.0007615109744957355</v>
+        <v>0.00244988357667919</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0003419302289088933</v>
+        <v>0.0006285543250523856</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0009017518011381093</v>
+        <v>0.0008750483230042183</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0008007844709441603</v>
+        <v>0.001466399648812788</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.00103527743000697</v>
+        <v>0.0003634202799992131</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.002096013321971171</v>
+        <v>0.001303329370407852</v>
       </c>
       <c r="CJ8" t="n">
         <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.001121733344578696</v>
+        <v>0.0006767182488808809</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0004645966738839991</v>
+        <v>0.0001775242273902328</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.001295291175473912</v>
+        <v>0.001244846011177608</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0007332852081176429</v>
+        <v>0.001624168130058315</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.002047909705636228</v>
+        <v>0.001748259615130104</v>
       </c>
       <c r="CP8" t="n">
-        <v>-1.582779360557174e-05</v>
+        <v>0.0001721153622118332</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.001178284532550367</v>
+        <v>0.002433573841683076</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.0003024413190908376</v>
+        <v>0.001866034049160509</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0.0004566535822823098</v>
+        <v>0.0007905900520746468</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.00012572382622964</v>
+        <v>0.001775248455471298</v>
       </c>
       <c r="CU8" t="n">
-        <v>-3.04092737210826e-05</v>
+        <v>0.0001592066076193277</v>
       </c>
       <c r="CV8" t="n">
-        <v>6.269516328462343e-05</v>
+        <v>8.015419362712163e-05</v>
       </c>
       <c r="CW8" t="n">
         <v>0</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.0005652900951901823</v>
+        <v>0.0003996617409139314</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.0007855946062920894</v>
+        <v>0.001042772489003854</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-5.986231667165498e-05</v>
+        <v>0.0002014962253910207</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0001796951465390745</v>
+        <v>0.0001422699968384678</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.001217811860405771</v>
+        <v>0.001200995363724664</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.001147146887375267</v>
+        <v>6.728286736906452e-05</v>
       </c>
       <c r="DD8" t="n">
-        <v>8.659881699024928e-05</v>
+        <v>0.0001923190333745106</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.00222640181468547</v>
+        <v>0.001305069790147684</v>
       </c>
       <c r="DF8" t="n">
-        <v>-4.489673750374124e-05</v>
+        <v>3.966364525219979e-05</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.001342714507753387</v>
+        <v>0.0007631086230952765</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.001591234377220665</v>
+        <v>0.0006627128951647882</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0005188582223478345</v>
+        <v>0.001145545769548278</v>
       </c>
       <c r="DJ8" t="n">
-        <v>-3.093102381690471e-05</v>
+        <v>0.0002483538947779529</v>
       </c>
       <c r="DK8" t="n">
-        <v>9.674298613348011e-05</v>
+        <v>0.0004779153178834317</v>
       </c>
       <c r="DL8" t="n">
+        <v>0.0008866247778067604</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0.0007943549320803156</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0.00288725559778136</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>0.0004282385396004756</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0.0006042418095207253</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>-8.010253123999499e-06</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>0.000485919422365605</v>
+      </c>
+      <c r="DS8" t="n">
         <v>0</v>
       </c>
-      <c r="DM8" t="n">
-        <v>0.0004823614471153315</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>8.197478178413043e-05</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>-0.0008718871806797313</v>
-      </c>
-      <c r="DP8" t="n">
-        <v>0.0005018903238060868</v>
-      </c>
-      <c r="DQ8" t="n">
+      <c r="DT8" t="n">
+        <v>0.001187732245489667</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0.0003009295139955903</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>2.245508982036404e-05</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0.0001860995411784278</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0.000384173056719686</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0.002694286883808008</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>4.607745102494787e-05</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0.002017403833793507</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0.0002424053859388986</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0.0005725803795588374</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0.0003403701665444792</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>2.37116661397474e-05</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0.001436162978590014</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>0.0003672358155410615</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0.00024469412365557</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0.0007546678372005233</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>0.0001340238426071783</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0.0007556929268092843</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>2.245508982036404e-05</v>
+      </c>
+      <c r="EM8" t="n">
         <v>0</v>
       </c>
-      <c r="DR8" t="n">
-        <v>0.0001747414781312101</v>
-      </c>
-      <c r="DS8" t="n">
-        <v>2.319826786266188e-05</v>
-      </c>
-      <c r="DT8" t="n">
-        <v>-0.000573545566106104</v>
-      </c>
-      <c r="DU8" t="n">
-        <v>0.0001032437397173319</v>
-      </c>
-      <c r="DV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW8" t="n">
-        <v>0.0001890023643454475</v>
-      </c>
-      <c r="DX8" t="n">
-        <v>0.0003802752131309955</v>
-      </c>
-      <c r="DY8" t="n">
-        <v>0.0006895346396270291</v>
-      </c>
-      <c r="DZ8" t="n">
-        <v>2.418574653337557e-05</v>
-      </c>
-      <c r="EA8" t="n">
-        <v>0.001138490241662343</v>
-      </c>
-      <c r="EB8" t="n">
-        <v>0.0006924546322826964</v>
-      </c>
-      <c r="EC8" t="n">
-        <v>0.0006141162094244951</v>
-      </c>
-      <c r="ED8" t="n">
-        <v>0.0008525554771832173</v>
-      </c>
-      <c r="EE8" t="n">
-        <v>0.0001120415347818232</v>
-      </c>
-      <c r="EF8" t="n">
-        <v>0.0005830466474798595</v>
-      </c>
-      <c r="EG8" t="n">
-        <v>0.0001492528782714192</v>
-      </c>
-      <c r="EH8" t="n">
-        <v>0.0002120408812999769</v>
-      </c>
-      <c r="EI8" t="n">
-        <v>0.0001151833208643927</v>
-      </c>
-      <c r="EJ8" t="n">
-        <v>0.0008594641860143942</v>
-      </c>
-      <c r="EK8" t="n">
-        <v>0.0005955614844368711</v>
-      </c>
-      <c r="EL8" t="n">
-        <v>2.387774594078129e-05</v>
-      </c>
-      <c r="EM8" t="n">
-        <v>0.0003501995548529397</v>
-      </c>
       <c r="EN8" t="n">
-        <v>0.0001747818045421595</v>
+        <v>-7.48502994011302e-06</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0002690290051465816</v>
+        <v>0.0008037980126543942</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0002048636846674723</v>
+        <v>0.00121531067075282</v>
       </c>
       <c r="ER8" t="n">
         <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.0001103121764674197</v>
+        <v>0.0001185583306987231</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0004106917293688727</v>
+        <v>0.0003412032667626186</v>
       </c>
       <c r="EU8" t="n">
-        <v>-6.344383852747437e-05</v>
+        <v>0.0001750997774264823</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.0001944288875346201</v>
+        <v>0.0001260631572484794</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0006356326930806094</v>
+        <v>0.0006510026938042479</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0002320471299245508</v>
+        <v>-0.0003738893985310854</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.0004799423567606709</v>
+        <v>0.0001002422783846768</v>
       </c>
     </row>
     <row r="9">
@@ -4490,466 +4490,466 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003682634730538936</v>
+        <v>0.004485741749439287</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00165447025135218</v>
+        <v>0.003682634730538947</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001483392454047083</v>
+        <v>0.0010817690104995</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002142857142857135</v>
+        <v>0.003413173652694634</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002718937717356951</v>
+        <v>0.001938775510204138</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006287425149700598</v>
+        <v>0.01143712574850303</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003913458479160003</v>
+        <v>0.007244897959183716</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002108843537414973</v>
+        <v>0.005627568763831847</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0009291893623838199</v>
+        <v>0.002514970059880273</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001257658819735563</v>
+        <v>0.001836734693877584</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0004454342984409277</v>
+        <v>0.00108843537414971</v>
       </c>
       <c r="M9" t="n">
-        <v>0.005986394557823138</v>
+        <v>0.005607177186799095</v>
       </c>
       <c r="N9" t="n">
-        <v>0.006696571611662894</v>
+        <v>0.008919485184076703</v>
       </c>
       <c r="O9" t="n">
-        <v>0.005599745466115147</v>
+        <v>0.003742514970059896</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001782871696911792</v>
+        <v>0.003149856824689767</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0267365269461078</v>
+        <v>0.01918587249326553</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001846545686087209</v>
+        <v>0.003909003524511378</v>
       </c>
       <c r="S9" t="n">
-        <v>0.006646706586826356</v>
+        <v>0.004806151874399233</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0004514672686229626</v>
+        <v>0.002736239261851714</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001391896071759946</v>
+        <v>0.002108843537415006</v>
       </c>
       <c r="V9" t="n">
-        <v>0.00557138334916113</v>
+        <v>0.006568407561678957</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001890419737263638</v>
+        <v>0.00237103492470363</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01302721088435375</v>
+        <v>0.0009291893623838643</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0008083832335329388</v>
+        <v>0.002823129251700718</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.009580838323353302</v>
+        <v>0.01134730538922158</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.007752170008979431</v>
+        <v>0.01727027835977257</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001409804549823723</v>
+        <v>0.0004514672686230514</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.003163265306122476</v>
+        <v>0.007731466751511285</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.007206928549334924</v>
+        <v>0.01187751314568515</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.01778533869471075</v>
+        <v>0.01639344262295087</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0103812880487023</v>
+        <v>0.01249599487343803</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001577482214661263</v>
+        <v>0.001359468858678514</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.001646706586826374</v>
+        <v>0.002178788849727664</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.01595238095238095</v>
+        <v>0.006360544217687103</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.02159564242230051</v>
+        <v>0.01919256648510093</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.02318606900999674</v>
+        <v>0.0313331271265079</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.002245508982035948</v>
+        <v>0.001896933291179315</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.02047904191616768</v>
+        <v>0.009640718562874273</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.0005258274048870693</v>
+        <v>0.004046791021182461</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.008537414965986413</v>
+        <v>0.005753170429941268</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0007369432874078097</v>
+        <v>0.002242870874719649</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.003161555485298784</v>
+        <v>0.006497005988023974</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.01741416640890809</v>
+        <v>0.009248376121249624</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.00704081632653063</v>
+        <v>0.001527203308940483</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.009625850340136077</v>
+        <v>0.002176870748299364</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.005544217687074848</v>
+        <v>0.001076289965178834</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.002068087814190234</v>
+        <v>0.005628742514970086</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.0005102040816326814</v>
+        <v>0.005186127903277105</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.001304486159719998</v>
+        <v>0.001972789115646312</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.001845370664969748</v>
+        <v>0.002784431137724597</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.006768707482993208</v>
+        <v>0.002690724912947084</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.01136054421768709</v>
+        <v>0.004517782761935307</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.009900672861262371</v>
+        <v>0.009248376121249634</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0009496676163343043</v>
+        <v>0.00091685109073667</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0005088296917090673</v>
+        <v>0.0006886227544910528</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.001972789115646256</v>
+        <v>0.003561807841963505</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.007346938775510214</v>
+        <v>0.008911564625850387</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.001655523718560947</v>
+        <v>0.004020259575815111</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.002904191616766483</v>
+        <v>0.00236526946107789</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.01431137724550901</v>
+        <v>0.01931137724550901</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.002849002849002835</v>
+        <v>0.006586826347305419</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.003877551020408166</v>
+        <v>0.002544148458545348</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001336302895322916</v>
+        <v>0.001700680272108901</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0003711722858026345</v>
+        <v>0.001802721088435399</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.002371034924703586</v>
+        <v>0.006258503401360594</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.004549823774431227</v>
+        <v>0.002455089820359302</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.003843537414966003</v>
+        <v>0.005671259211791113</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>8.982035928145615e-05</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.009149659863945591</v>
+        <v>0.0153401360544218</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.002214905716851246</v>
+        <v>0.001972637607381456</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.001249599487343756</v>
+        <v>0.002993197278911597</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.008809523809523812</v>
+        <v>0.005058365758754934</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.001281640499839742</v>
+        <v>0.005248182105595989</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0002863506204262678</v>
+        <v>0.0003183699458771949</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.002338993912207587</v>
+        <v>0.0004806151874399256</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.003443113772455098</v>
+        <v>0.002845399936768933</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.002874251497005998</v>
+        <v>0.004293495674463343</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0007954183900731549</v>
+        <v>0.00350299401197608</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.005884353741496628</v>
+        <v>0.004850299401197644</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.00163265306122452</v>
+        <v>0.003775510204081678</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.00320359281437127</v>
+        <v>0.007335329341317398</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.002371166613974107</v>
+        <v>0.003140019224607504</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.002819609099647535</v>
+        <v>0.005408845052497602</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.004081632653061251</v>
+        <v>0.002531239987183609</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.003741496598639471</v>
+        <v>0.002149857730003213</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.003435374149659865</v>
+        <v>0.003639455782312972</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0002845399936769355</v>
+        <v>0.000239520958083872</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.003684716437039381</v>
+        <v>0.002499198974687611</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.002971862156180882</v>
+        <v>0.004521024343977264</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.003075937199615453</v>
+        <v>0.001763068357562658</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.00143669560011972</v>
+        <v>0.002544910179640758</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.003716757449535357</v>
+        <v>0.002724550898203626</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0002213088839709498</v>
+        <v>0.0003477711033828878</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.004940119760479045</v>
+        <v>0.008010253123998713</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.003332265299583415</v>
+        <v>0.005607177186799106</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.0004190362167015849</v>
+        <v>0.001986542774751687</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.0008330663248958259</v>
+        <v>0.004615871008536243</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>0.0004790419161676995</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0004081632653061273</v>
+        <v>0.0002395209580838609</v>
       </c>
       <c r="CW9" t="n">
-        <v>0</v>
+        <v>2.994011976048538e-05</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.001687360713148667</v>
+        <v>0.001330034024126214</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.002844311377245523</v>
+        <v>0.007978212111502713</v>
       </c>
       <c r="CZ9" t="n">
-        <v>6.40820249919738e-05</v>
+        <v>0.0002993115833582749</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.001017659383418135</v>
+        <v>0.0008163265306122991</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.001556420233463029</v>
+        <v>0.003043896187119532</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.001972637607381434</v>
+        <v>0.003396347324575466</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.001632653061224498</v>
+        <v>0.0002902289584005402</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.003920981741993501</v>
+        <v>0.003941044537007365</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.001463569837734624</v>
+        <v>0.0007369432874078762</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.001453758119393711</v>
+        <v>0.002979814162127537</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.00583832335329344</v>
+        <v>0.001347305389221598</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.001556886227544929</v>
+        <v>0.002036271078587315</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.001377245508982039</v>
+        <v>0.002114706824735679</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.001537968599807704</v>
+        <v>0.001975456450164614</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.001484689143210582</v>
+        <v>0.001106544419854594</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0007423445716052912</v>
+        <v>0.003023952095808413</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.001707239962061347</v>
+        <v>0.007245508982035953</v>
       </c>
       <c r="DO9" t="n">
-        <v>-3.224766204451557e-05</v>
+        <v>0.002499198974687622</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.001336302895322916</v>
+        <v>0.003635788808093609</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0006367398917542011</v>
+        <v>0.0007114135477884531</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.00143712574850301</v>
+        <v>0.001666666666666716</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0002994011976048316</v>
+        <v>9.612303748798289e-05</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.001570009612303702</v>
+        <v>0.006676646706586864</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.002655706607650965</v>
+        <v>0.003825482137211544</v>
       </c>
       <c r="DV9" t="n">
-        <v>3.093102381688251e-05</v>
+        <v>6.363347120585949e-05</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0005876894525208342</v>
+        <v>0.001190476190476242</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.001858378724767673</v>
+        <v>0.001946107784431184</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.002883691124639498</v>
+        <v>0.008502994011976095</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.000340241261985752</v>
+        <v>0.0002865329512894421</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.002784431137724563</v>
+        <v>0.002843460041903623</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.003983559911476487</v>
+        <v>0.002381688833900419</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.001979585524280803</v>
+        <v>0.001549162187796438</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.002514970059880251</v>
+        <v>0.001634091637295765</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0007784431137724757</v>
+        <v>0.0003844921499519427</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.001347305389221565</v>
+        <v>0.002082665812239659</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0005876894525208454</v>
+        <v>0.0007597340930674323</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0005567584287039628</v>
+        <v>0.000419161676646751</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.002755527074655528</v>
+        <v>0.003332265299583481</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.000923272843043621</v>
+        <v>0.002050624799743661</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.001856287425149727</v>
+        <v>0.001114294810569905</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0001272669424116857</v>
+        <v>0.0001602050624799789</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0005988023952096077</v>
+        <v>0.0006122448979592355</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.0003711722858026234</v>
+        <v>0.00107752170008979</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.001794296699775666</v>
+        <v>0.00237416904083565</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.003876962512015358</v>
+        <v>0.002082665812239681</v>
       </c>
       <c r="ER9" t="n">
-        <v>5.988023952097077e-05</v>
+        <v>0.0002563280999679729</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0003891050583657574</v>
+        <v>0.0003892215568862767</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.002125748502994029</v>
+        <v>0.001719197707736431</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.001616766467065878</v>
+        <v>0.004311377245508996</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0003292427416941024</v>
+        <v>0.0003591739000299299</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.002574850299401221</v>
+        <v>0.004005126561999373</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0008330663248958037</v>
+        <v>0.0009291893623838754</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.001292517006802718</v>
+        <v>0.0006681514476614359</v>
       </c>
     </row>
   </sheetData>
